--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A64930C-1E14-6B49-8075-AA648C94FCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C299BFEE-A384-6B4C-80CC-075AF18A9961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
     <sheet name="Vol.2" sheetId="2" r:id="rId2"/>
     <sheet name="Vol.3" sheetId="3" r:id="rId3"/>
     <sheet name="Vol.4" sheetId="4" r:id="rId4"/>
+    <sheet name="Vol.5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="243">
   <si>
     <t>No.</t>
   </si>
@@ -34,6 +35,579 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>待つ</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>重さ</t>
+  </si>
+  <si>
+    <t>heard</t>
+  </si>
+  <si>
+    <t>聞いた</t>
+  </si>
+  <si>
+    <t>herd</t>
+  </si>
+  <si>
+    <t>群（む）れ</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+  <si>
+    <t>日々</t>
+  </si>
+  <si>
+    <t>daze</t>
+  </si>
+  <si>
+    <t>ぼんやり</t>
+  </si>
+  <si>
+    <t>heel</t>
+  </si>
+  <si>
+    <t>かかと</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>治（なお）る</t>
+  </si>
+  <si>
+    <t>peak</t>
+  </si>
+  <si>
+    <t>頂上（ちょうじょう）</t>
+  </si>
+  <si>
+    <t>peek</t>
+  </si>
+  <si>
+    <t>のぞき見</t>
+  </si>
+  <si>
+    <t>sent</t>
+  </si>
+  <si>
+    <t>送った</t>
+  </si>
+  <si>
+    <t>cent</t>
+  </si>
+  <si>
+    <t>セント</t>
+  </si>
+  <si>
+    <t>scent</t>
+  </si>
+  <si>
+    <t>におい</t>
+  </si>
+  <si>
+    <t>feet</t>
+  </si>
+  <si>
+    <t>足</t>
+  </si>
+  <si>
+    <t>feat</t>
+  </si>
+  <si>
+    <t>てがら</t>
+  </si>
+  <si>
+    <t>vain</t>
+  </si>
+  <si>
+    <t>うぬぼれた</t>
+  </si>
+  <si>
+    <t>vane</t>
+  </si>
+  <si>
+    <t>羽根</t>
+  </si>
+  <si>
+    <t>vein</t>
+  </si>
+  <si>
+    <t>miner</t>
+  </si>
+  <si>
+    <t>鉱夫（こうふ）</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>重要（じゅうよう）でない</t>
+  </si>
+  <si>
+    <t>allowed</t>
+  </si>
+  <si>
+    <t>許（ゆる）された</t>
+  </si>
+  <si>
+    <t>aloud</t>
+  </si>
+  <si>
+    <t>声に出して</t>
+  </si>
+  <si>
+    <t>who's</t>
+  </si>
+  <si>
+    <t>だれ（"who is"を短くした言葉）</t>
+  </si>
+  <si>
+    <t>whose</t>
+  </si>
+  <si>
+    <t>だれの</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>西</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>急な・けわしい</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>メンバー・会員</t>
+  </si>
+  <si>
+    <t>gleam</t>
+  </si>
+  <si>
+    <t>きらめく・かがやく</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>新しい・新（しん）せんな</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>スピード・速さ</t>
+  </si>
+  <si>
+    <t>steam</t>
+  </si>
+  <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
+    <t>beast</t>
+  </si>
+  <si>
+    <t>けもの</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>speck</t>
+  </si>
+  <si>
+    <t>小さな点・しみ</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>持っていた</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>〜のふりをする</t>
+  </si>
+  <si>
+    <t>greed</t>
+  </si>
+  <si>
+    <t>ほしがりすぎること</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>たな</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>もっとも少ない</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>ねっしんな</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>chief</t>
+  </si>
+  <si>
+    <t>おもな・長</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>全部終わる・かんせいする</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>そで</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>エンジン</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技術（ぎじゅつ）</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>犯罪（はんざい）</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>すりつぶす</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>今夜（こんや）</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>レンガ</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光（ひかり）・軽（かる）い</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>住（す）む・生（い）きる</t>
+  </si>
+  <si>
+    <t>chill</t>
+  </si>
+  <si>
+    <t>冷（ひ）え・寒気（さむけ）</t>
+  </si>
+  <si>
+    <t>delight</t>
+  </si>
+  <si>
+    <t>大喜（おおよろこ）び</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>建（た）てる</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>みぞ</t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>決（き）める</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>目撃者（もくげきしゃ）</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>風（かぜ）・巻（ま）く</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>地区（ちく）</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>インチ</t>
+  </si>
+  <si>
+    <t>sigh</t>
+  </si>
+  <si>
+    <t>ため息</t>
+  </si>
+  <si>
+    <t>fright</t>
+  </si>
+  <si>
+    <t>恐怖（きょうふ）</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>思（おも）い出（だ）させる</t>
+  </si>
+  <si>
+    <t>splice</t>
+  </si>
+  <si>
+    <t>つなぎ合（あ）わせる</t>
+  </si>
+  <si>
+    <t>spinning</t>
+  </si>
+  <si>
+    <t>回転（かいてん）</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>チケット・切符（きっぷ）</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>驚（おどろ）き</t>
+  </si>
+  <si>
+    <t>brighten</t>
+  </si>
+  <si>
+    <t>明（あか）るくする</t>
+  </si>
+  <si>
     <t>block</t>
   </si>
   <si>
@@ -103,6 +677,9 @@
     <t>host</t>
   </si>
   <si>
+    <t>主人（しゅじん）</t>
+  </si>
+  <si>
     <t>online</t>
   </si>
   <si>
@@ -148,6 +725,9 @@
     <t>globe</t>
   </si>
   <si>
+    <t>地球（ちきゅう）</t>
+  </si>
+  <si>
     <t>borrow</t>
   </si>
   <si>
@@ -172,442 +752,7 @@
     <t>医者</t>
   </si>
   <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>steep</t>
-  </si>
-  <si>
-    <t>急な・けわしい</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>メンバー・会員</t>
-  </si>
-  <si>
-    <t>gleam</t>
-  </si>
-  <si>
-    <t>きらめく・かがやく</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>新しい・新（しん）せんな</t>
-  </si>
-  <si>
-    <t>freedom</t>
-  </si>
-  <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>スピード・速さ</t>
-  </si>
-  <si>
-    <t>steam</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
-  </si>
-  <si>
-    <t>beast</t>
-  </si>
-  <si>
-    <t>けもの</t>
-  </si>
-  <si>
-    <t>believe</t>
-  </si>
-  <si>
-    <t>しんじる</t>
-  </si>
-  <si>
-    <t>speck</t>
-  </si>
-  <si>
-    <t>小さな点・しみ</t>
-  </si>
-  <si>
-    <t>kept</t>
-  </si>
-  <si>
-    <t>持っていた</t>
-  </si>
-  <si>
-    <t>cheap</t>
-  </si>
-  <si>
-    <t>安い</t>
-  </si>
-  <si>
-    <t>pretend</t>
-  </si>
-  <si>
-    <t>〜のふりをする</t>
-  </si>
-  <si>
-    <t>greed</t>
-  </si>
-  <si>
-    <t>ほしがりすぎること</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>たな</t>
-  </si>
-  <si>
-    <t>least</t>
-  </si>
-  <si>
-    <t>もっとも少ない</t>
-  </si>
-  <si>
-    <t>eager</t>
-  </si>
-  <si>
-    <t>ねっしんな</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>理由</t>
-  </si>
-  <si>
-    <t>chief</t>
-  </si>
-  <si>
-    <t>おもな・長</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
-    <t>全部終わる・かんせいする</t>
-  </si>
-  <si>
-    <t>sleeve</t>
-  </si>
-  <si>
-    <t>そで</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>エンジン</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>守る</t>
-  </si>
-  <si>
-    <t>skill</t>
-  </si>
-  <si>
-    <t>技術（ぎじゅつ）</t>
-  </si>
-  <si>
-    <t>crime</t>
-  </si>
-  <si>
-    <t>犯罪（はんざい）</t>
-  </si>
-  <si>
-    <t>grind</t>
-  </si>
-  <si>
-    <t>すりつぶす</t>
-  </si>
-  <si>
-    <t>tonight</t>
-  </si>
-  <si>
-    <t>今夜（こんや）</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>レンガ</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
-    <t>光（ひかり）・軽（かる）い</t>
-  </si>
-  <si>
-    <t>live</t>
-  </si>
-  <si>
-    <t>住（す）む・生（い）きる</t>
-  </si>
-  <si>
-    <t>chill</t>
-  </si>
-  <si>
-    <t>冷（ひ）え・寒気（さむけ）</t>
-  </si>
-  <si>
-    <t>delight</t>
-  </si>
-  <si>
-    <t>大喜（おおよろこ）び</t>
-  </si>
-  <si>
-    <t>build</t>
-  </si>
-  <si>
-    <t>建（た）てる</t>
-  </si>
-  <si>
-    <t>ditch</t>
-  </si>
-  <si>
-    <t>みぞ</t>
-  </si>
-  <si>
-    <t>decide</t>
-  </si>
-  <si>
-    <t>決（き）める</t>
-  </si>
-  <si>
-    <t>witness</t>
-  </si>
-  <si>
-    <t>目撃者（もくげきしゃ）</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>風（かぜ）・巻（ま）く</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>地区（ちく）</t>
-  </si>
-  <si>
-    <t>inch</t>
-  </si>
-  <si>
-    <t>インチ</t>
-  </si>
-  <si>
-    <t>sigh</t>
-  </si>
-  <si>
-    <t>ため息</t>
-  </si>
-  <si>
-    <t>fright</t>
-  </si>
-  <si>
-    <t>恐怖（きょうふ）</t>
-  </si>
-  <si>
-    <t>remind</t>
-  </si>
-  <si>
-    <t>思（おも）い出（だ）させる</t>
-  </si>
-  <si>
-    <t>splice</t>
-  </si>
-  <si>
-    <t>つなぎ合（あ）わせる</t>
-  </si>
-  <si>
-    <t>spinning</t>
-  </si>
-  <si>
-    <t>回転（かいてん）</t>
-  </si>
-  <si>
-    <t>ticket</t>
-  </si>
-  <si>
-    <t>チケット・切符（きっぷ）</t>
-  </si>
-  <si>
-    <t>surprise</t>
-  </si>
-  <si>
-    <t>驚（おどろ）き</t>
-  </si>
-  <si>
-    <t>brighten</t>
-  </si>
-  <si>
-    <t>明（あか）るくする</t>
-  </si>
-  <si>
-    <t>主人（しゅじん）</t>
-  </si>
-  <si>
-    <t>地球（ちきゅう）</t>
+    <t>静脈（せいみゃく）、血管（けっかん）</t>
   </si>
 </sst>
 </file>
@@ -1006,10 +1151,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1017,10 +1162,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1028,10 +1173,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1039,10 +1184,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1050,10 +1195,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1061,10 +1206,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1072,10 +1217,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1083,10 +1228,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1094,10 +1239,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1105,10 +1250,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1116,10 +1261,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1127,10 +1272,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1138,10 +1283,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,10 +1294,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,10 +1305,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,10 +1316,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1182,10 +1327,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1193,10 +1338,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1204,10 +1349,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1215,10 +1360,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1226,10 +1371,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1237,10 +1382,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1248,10 +1393,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1259,10 +1404,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1291,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1302,10 +1447,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1313,10 +1458,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1324,10 +1469,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1335,10 +1480,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1346,10 +1491,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1357,10 +1502,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1368,10 +1513,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1379,10 +1524,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1390,10 +1535,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1401,10 +1546,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1412,10 +1557,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1423,10 +1568,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1434,10 +1579,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1445,10 +1590,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1456,10 +1601,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1467,10 +1612,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1478,10 +1623,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1489,10 +1634,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1500,10 +1645,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1511,10 +1656,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1522,10 +1667,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1533,10 +1678,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1544,10 +1689,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1576,10 +1721,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,10 +1732,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1598,10 +1743,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1609,10 +1754,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1620,10 +1765,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1631,10 +1776,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1642,10 +1787,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1653,10 +1798,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1664,10 +1809,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1675,10 +1820,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1686,10 +1831,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1697,10 +1842,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1708,10 +1853,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1719,10 +1864,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1730,10 +1875,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1741,10 +1886,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1752,10 +1897,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1763,10 +1908,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1774,10 +1919,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1785,10 +1930,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1796,10 +1941,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1807,10 +1952,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1818,10 +1963,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1829,10 +1974,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1861,10 +2006,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1872,10 +2017,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1883,10 +2028,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1894,10 +2039,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1905,10 +2050,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1916,10 +2061,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1927,10 +2072,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1938,10 +2083,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1949,10 +2094,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1960,10 +2105,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1971,10 +2116,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>214</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1982,10 +2127,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1993,10 +2138,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2004,10 +2149,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2015,10 +2160,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>222</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2026,10 +2171,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2037,10 +2182,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2048,10 +2193,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>228</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2059,10 +2204,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2070,10 +2215,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2081,10 +2226,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>234</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2092,10 +2237,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2103,10 +2248,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2114,10 +2259,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C299BFEE-A384-6B4C-80CC-075AF18A9961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9796071-0D95-CF42-A618-71305AFFA93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="Vol.3" sheetId="3" r:id="rId3"/>
     <sheet name="Vol.4" sheetId="4" r:id="rId4"/>
     <sheet name="Vol.5" sheetId="5" r:id="rId5"/>
+    <sheet name="Vol.6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="291">
   <si>
     <t>No.</t>
   </si>
@@ -35,6 +36,720 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>bunch</t>
+  </si>
+  <si>
+    <t>束（たば）・房（ふさ）</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>果物（くだもの）</t>
+  </si>
+  <si>
+    <t>argue</t>
+  </si>
+  <si>
+    <t>crumb</t>
+  </si>
+  <si>
+    <t>パンくず</t>
+  </si>
+  <si>
+    <t>crew</t>
+  </si>
+  <si>
+    <t>乗組員</t>
+  </si>
+  <si>
+    <t>tune</t>
+  </si>
+  <si>
+    <t>曲</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>ジュース</t>
+  </si>
+  <si>
+    <t>refuse</t>
+  </si>
+  <si>
+    <t>断（ことわ）る</t>
+  </si>
+  <si>
+    <t>truth</t>
+  </si>
+  <si>
+    <t>真実</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>若（わか）い</t>
+  </si>
+  <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>手がかり</t>
+  </si>
+  <si>
+    <t>trunk</t>
+  </si>
+  <si>
+    <t>幹（みき）</t>
+  </si>
+  <si>
+    <t>amuse</t>
+  </si>
+  <si>
+    <t>楽しませる</t>
+  </si>
+  <si>
+    <t>suit</t>
+  </si>
+  <si>
+    <t>スーツ</t>
+  </si>
+  <si>
+    <t>rude</t>
+  </si>
+  <si>
+    <t>失（しつ）礼な</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>信（しん）じる</t>
+  </si>
+  <si>
+    <t>stuck</t>
+  </si>
+  <si>
+    <t>動けなくなった</t>
+  </si>
+  <si>
+    <t>rescue</t>
+  </si>
+  <si>
+    <t>助ける</t>
+  </si>
+  <si>
+    <t>dew</t>
+  </si>
+  <si>
+    <t>つゆ</t>
+  </si>
+  <si>
+    <t>brush</t>
+  </si>
+  <si>
+    <t>ブラシ</t>
+  </si>
+  <si>
+    <t>undercover</t>
+  </si>
+  <si>
+    <t>bruise</t>
+  </si>
+  <si>
+    <t>あざ</t>
+  </si>
+  <si>
+    <t>accuse</t>
+  </si>
+  <si>
+    <t>責（せ）める</t>
+  </si>
+  <si>
+    <t>stew</t>
+  </si>
+  <si>
+    <t>シチュー</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>西</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>急な・けわしい</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>メンバー・会員</t>
+  </si>
+  <si>
+    <t>gleam</t>
+  </si>
+  <si>
+    <t>きらめく・かがやく</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>新しい・新（しん）せんな</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>スピード・速さ</t>
+  </si>
+  <si>
+    <t>steam</t>
+  </si>
+  <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
+    <t>beast</t>
+  </si>
+  <si>
+    <t>けもの</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>speck</t>
+  </si>
+  <si>
+    <t>小さな点・しみ</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>持っていた</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>〜のふりをする</t>
+  </si>
+  <si>
+    <t>greed</t>
+  </si>
+  <si>
+    <t>ほしがりすぎること</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>たな</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>もっとも少ない</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>ねっしんな</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>chief</t>
+  </si>
+  <si>
+    <t>おもな・長</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>全部終わる・かんせいする</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>そで</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>エンジン</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技術（ぎじゅつ）</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>犯罪（はんざい）</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>すりつぶす</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>今夜（こんや）</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>レンガ</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光（ひかり）・軽（かる）い</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>住（す）む・生（い）きる</t>
+  </si>
+  <si>
+    <t>chill</t>
+  </si>
+  <si>
+    <t>冷（ひ）え・寒気（さむけ）</t>
+  </si>
+  <si>
+    <t>delight</t>
+  </si>
+  <si>
+    <t>大喜（おおよろこ）び</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>建（た）てる</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>みぞ</t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>決（き）める</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>目撃者（もくげきしゃ）</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>風（かぜ）・巻（ま）く</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>地区（ちく）</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>インチ</t>
+  </si>
+  <si>
+    <t>sigh</t>
+  </si>
+  <si>
+    <t>ため息</t>
+  </si>
+  <si>
+    <t>fright</t>
+  </si>
+  <si>
+    <t>恐怖（きょうふ）</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>思（おも）い出（だ）させる</t>
+  </si>
+  <si>
+    <t>splice</t>
+  </si>
+  <si>
+    <t>つなぎ合（あ）わせる</t>
+  </si>
+  <si>
+    <t>spinning</t>
+  </si>
+  <si>
+    <t>回転（かいてん）</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>チケット・切符（きっぷ）</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>驚（おどろ）き</t>
+  </si>
+  <si>
+    <t>brighten</t>
+  </si>
+  <si>
+    <t>明（あか）るくする</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>ブロック・じゃまする</t>
+  </si>
+  <si>
+    <t>shown</t>
+  </si>
+  <si>
+    <t>見せた</t>
+  </si>
+  <si>
+    <t>oatmeal</t>
+  </si>
+  <si>
+    <t>オートミール</t>
+  </si>
+  <si>
+    <t>wrote</t>
+  </si>
+  <si>
+    <t>書いた</t>
+  </si>
+  <si>
+    <t>fellow</t>
+  </si>
+  <si>
+    <t>仲（なか）間</t>
+  </si>
+  <si>
+    <t>scold</t>
+  </si>
+  <si>
+    <t>しかる</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>海岸</t>
+  </si>
+  <si>
+    <t>odd</t>
+  </si>
+  <si>
+    <t>変（へん）な</t>
+  </si>
+  <si>
+    <t>locate</t>
+  </si>
+  <si>
+    <t>見つける</t>
+  </si>
+  <si>
+    <t>slope</t>
+  </si>
+  <si>
+    <t>坂</t>
+  </si>
+  <si>
+    <t>throat</t>
+  </si>
+  <si>
+    <t>のど</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>主人（しゅじん）</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>オンライン</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>しょうげき</t>
+  </si>
+  <si>
+    <t>solve</t>
+  </si>
+  <si>
+    <t>解（と）く</t>
+  </si>
+  <si>
+    <t>known</t>
+  </si>
+  <si>
+    <t>知られた</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>在（ざい）庫</t>
+  </si>
+  <si>
+    <t>boast</t>
+  </si>
+  <si>
+    <t>じまんする</t>
+  </si>
+  <si>
+    <t>globe</t>
+  </si>
+  <si>
+    <t>地球（ちきゅう）</t>
+  </si>
+  <si>
+    <t>borrow</t>
+  </si>
+  <si>
+    <t>借（か）りる</t>
+  </si>
+  <si>
+    <t>compose</t>
+  </si>
+  <si>
+    <t>作曲する</t>
+  </si>
+  <si>
+    <t>rocket</t>
+  </si>
+  <si>
+    <t>ロケット</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>医者</t>
+  </si>
+  <si>
     <t>wait</t>
   </si>
   <si>
@@ -140,6 +855,9 @@
     <t>vein</t>
   </si>
   <si>
+    <t>静脈（せいみゃく）、血管（けっかん）</t>
+  </si>
+  <si>
     <t>miner</t>
   </si>
   <si>
@@ -176,583 +894,10 @@
     <t>だれの</t>
   </si>
   <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>steep</t>
-  </si>
-  <si>
-    <t>急な・けわしい</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>メンバー・会員</t>
-  </si>
-  <si>
-    <t>gleam</t>
-  </si>
-  <si>
-    <t>きらめく・かがやく</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>新しい・新（しん）せんな</t>
-  </si>
-  <si>
-    <t>freedom</t>
-  </si>
-  <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>スピード・速さ</t>
-  </si>
-  <si>
-    <t>steam</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
-  </si>
-  <si>
-    <t>beast</t>
-  </si>
-  <si>
-    <t>けもの</t>
-  </si>
-  <si>
-    <t>believe</t>
-  </si>
-  <si>
-    <t>しんじる</t>
-  </si>
-  <si>
-    <t>speck</t>
-  </si>
-  <si>
-    <t>小さな点・しみ</t>
-  </si>
-  <si>
-    <t>kept</t>
-  </si>
-  <si>
-    <t>持っていた</t>
-  </si>
-  <si>
-    <t>cheap</t>
-  </si>
-  <si>
-    <t>安い</t>
-  </si>
-  <si>
-    <t>pretend</t>
-  </si>
-  <si>
-    <t>〜のふりをする</t>
-  </si>
-  <si>
-    <t>greed</t>
-  </si>
-  <si>
-    <t>ほしがりすぎること</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>たな</t>
-  </si>
-  <si>
-    <t>least</t>
-  </si>
-  <si>
-    <t>もっとも少ない</t>
-  </si>
-  <si>
-    <t>eager</t>
-  </si>
-  <si>
-    <t>ねっしんな</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>理由</t>
-  </si>
-  <si>
-    <t>chief</t>
-  </si>
-  <si>
-    <t>おもな・長</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
-    <t>全部終わる・かんせいする</t>
-  </si>
-  <si>
-    <t>sleeve</t>
-  </si>
-  <si>
-    <t>そで</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>エンジン</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>守る</t>
-  </si>
-  <si>
-    <t>skill</t>
-  </si>
-  <si>
-    <t>技術（ぎじゅつ）</t>
-  </si>
-  <si>
-    <t>crime</t>
-  </si>
-  <si>
-    <t>犯罪（はんざい）</t>
-  </si>
-  <si>
-    <t>grind</t>
-  </si>
-  <si>
-    <t>すりつぶす</t>
-  </si>
-  <si>
-    <t>tonight</t>
-  </si>
-  <si>
-    <t>今夜（こんや）</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>レンガ</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
-    <t>光（ひかり）・軽（かる）い</t>
-  </si>
-  <si>
-    <t>live</t>
-  </si>
-  <si>
-    <t>住（す）む・生（い）きる</t>
-  </si>
-  <si>
-    <t>chill</t>
-  </si>
-  <si>
-    <t>冷（ひ）え・寒気（さむけ）</t>
-  </si>
-  <si>
-    <t>delight</t>
-  </si>
-  <si>
-    <t>大喜（おおよろこ）び</t>
-  </si>
-  <si>
-    <t>build</t>
-  </si>
-  <si>
-    <t>建（た）てる</t>
-  </si>
-  <si>
-    <t>ditch</t>
-  </si>
-  <si>
-    <t>みぞ</t>
-  </si>
-  <si>
-    <t>decide</t>
-  </si>
-  <si>
-    <t>決（き）める</t>
-  </si>
-  <si>
-    <t>witness</t>
-  </si>
-  <si>
-    <t>目撃者（もくげきしゃ）</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>風（かぜ）・巻（ま）く</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>地区（ちく）</t>
-  </si>
-  <si>
-    <t>inch</t>
-  </si>
-  <si>
-    <t>インチ</t>
-  </si>
-  <si>
-    <t>sigh</t>
-  </si>
-  <si>
-    <t>ため息</t>
-  </si>
-  <si>
-    <t>fright</t>
-  </si>
-  <si>
-    <t>恐怖（きょうふ）</t>
-  </si>
-  <si>
-    <t>remind</t>
-  </si>
-  <si>
-    <t>思（おも）い出（だ）させる</t>
-  </si>
-  <si>
-    <t>splice</t>
-  </si>
-  <si>
-    <t>つなぎ合（あ）わせる</t>
-  </si>
-  <si>
-    <t>spinning</t>
-  </si>
-  <si>
-    <t>回転（かいてん）</t>
-  </si>
-  <si>
-    <t>ticket</t>
-  </si>
-  <si>
-    <t>チケット・切符（きっぷ）</t>
-  </si>
-  <si>
-    <t>surprise</t>
-  </si>
-  <si>
-    <t>驚（おどろ）き</t>
-  </si>
-  <si>
-    <t>brighten</t>
-  </si>
-  <si>
-    <t>明（あか）るくする</t>
-  </si>
-  <si>
-    <t>block</t>
-  </si>
-  <si>
-    <t>ブロック・じゃまする</t>
-  </si>
-  <si>
-    <t>shown</t>
-  </si>
-  <si>
-    <t>見せた</t>
-  </si>
-  <si>
-    <t>oatmeal</t>
-  </si>
-  <si>
-    <t>オートミール</t>
-  </si>
-  <si>
-    <t>wrote</t>
-  </si>
-  <si>
-    <t>書いた</t>
-  </si>
-  <si>
-    <t>fellow</t>
-  </si>
-  <si>
-    <t>仲（なか）間</t>
-  </si>
-  <si>
-    <t>scold</t>
-  </si>
-  <si>
-    <t>しかる</t>
-  </si>
-  <si>
-    <t>coast</t>
-  </si>
-  <si>
-    <t>海岸</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>変（へん）な</t>
-  </si>
-  <si>
-    <t>locate</t>
-  </si>
-  <si>
-    <t>見つける</t>
-  </si>
-  <si>
-    <t>slope</t>
-  </si>
-  <si>
-    <t>坂</t>
-  </si>
-  <si>
-    <t>throat</t>
-  </si>
-  <si>
-    <t>のど</t>
-  </si>
-  <si>
-    <t>host</t>
-  </si>
-  <si>
-    <t>主人（しゅじん）</t>
-  </si>
-  <si>
-    <t>online</t>
-  </si>
-  <si>
-    <t>オンライン</t>
-  </si>
-  <si>
-    <t>shock</t>
-  </si>
-  <si>
-    <t>しょうげき</t>
-  </si>
-  <si>
-    <t>solve</t>
-  </si>
-  <si>
-    <t>解（と）く</t>
-  </si>
-  <si>
-    <t>known</t>
-  </si>
-  <si>
-    <t>知られた</t>
-  </si>
-  <si>
-    <t>remote</t>
-  </si>
-  <si>
-    <t>遠い</t>
-  </si>
-  <si>
-    <t>stock</t>
-  </si>
-  <si>
-    <t>在（ざい）庫</t>
-  </si>
-  <si>
-    <t>boast</t>
-  </si>
-  <si>
-    <t>じまんする</t>
-  </si>
-  <si>
-    <t>globe</t>
-  </si>
-  <si>
-    <t>地球（ちきゅう）</t>
-  </si>
-  <si>
-    <t>borrow</t>
-  </si>
-  <si>
-    <t>借（か）りる</t>
-  </si>
-  <si>
-    <t>compose</t>
-  </si>
-  <si>
-    <t>作曲する</t>
-  </si>
-  <si>
-    <t>rocket</t>
-  </si>
-  <si>
-    <t>ロケット</t>
-  </si>
-  <si>
-    <t>doctor</t>
-  </si>
-  <si>
-    <t>医者</t>
-  </si>
-  <si>
-    <t>静脈（せいみゃく）、血管（けっかん）</t>
+    <t>議論（ぎろん）する</t>
+  </si>
+  <si>
+    <t>秘密（ひみつ）の</t>
   </si>
 </sst>
 </file>
@@ -1151,10 +1296,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1162,10 +1307,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1173,10 +1318,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
         <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1184,10 +1329,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1195,10 +1340,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1206,10 +1351,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1217,10 +1362,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
         <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1228,10 +1373,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1239,10 +1384,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1250,10 +1395,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
         <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1261,10 +1406,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
         <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1272,10 +1417,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
         <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1283,10 +1428,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
         <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1294,10 +1439,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
         <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1305,10 +1450,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
         <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1316,10 +1461,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
         <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1327,10 +1472,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
         <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1338,10 +1483,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
         <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1349,10 +1494,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
         <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1360,10 +1505,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
         <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1371,10 +1516,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
         <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1382,10 +1527,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
         <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1393,10 +1538,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
         <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1404,10 +1549,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1436,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1447,10 +1592,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1458,10 +1603,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1469,10 +1614,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1480,10 +1625,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1491,10 +1636,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1502,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1513,10 +1658,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1524,10 +1669,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1535,10 +1680,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1546,10 +1691,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1557,10 +1702,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1568,10 +1713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1579,10 +1724,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1590,10 +1735,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1601,10 +1746,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1612,10 +1757,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1623,10 +1768,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1634,10 +1779,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1645,10 +1790,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1656,10 +1801,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1667,10 +1812,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1678,10 +1823,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1689,10 +1834,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1721,10 +1866,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1732,10 +1877,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1743,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1754,10 +1899,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1765,10 +1910,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1776,10 +1921,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1787,10 +1932,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1798,10 +1943,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1809,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1820,10 +1965,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,10 +1976,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1842,10 +1987,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1853,10 +1998,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1864,10 +2009,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1875,10 +2020,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1886,10 +2031,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1897,10 +2042,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1908,10 +2053,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1919,10 +2064,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1930,10 +2075,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1941,10 +2086,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1952,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,10 +2108,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1974,10 +2119,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2006,10 +2151,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2017,10 +2162,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2028,10 +2173,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2039,10 +2184,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2050,10 +2195,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2061,10 +2206,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2072,10 +2217,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2083,10 +2228,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2094,10 +2239,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2105,10 +2250,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2116,10 +2261,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2127,10 +2272,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2138,10 +2283,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2149,10 +2294,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2160,10 +2305,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2171,10 +2316,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2182,10 +2327,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2193,10 +2338,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2204,10 +2349,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2215,10 +2360,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2226,10 +2371,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2237,10 +2382,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2248,10 +2393,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2259,10 +2404,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2291,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2302,10 +2447,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2313,10 +2458,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2324,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2335,10 +2480,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2346,10 +2491,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2357,10 +2502,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2368,10 +2513,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2379,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2390,10 +2535,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2401,10 +2546,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>261</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2412,10 +2557,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>263</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2423,10 +2568,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2434,10 +2579,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2445,10 +2590,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>269</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2456,10 +2601,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2467,10 +2612,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>273</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2478,10 +2623,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>275</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2489,10 +2634,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>277</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2500,10 +2645,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2511,10 +2656,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>281</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2522,10 +2667,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>283</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2533,10 +2678,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>285</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2544,10 +2689,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9796071-0D95-CF42-A618-71305AFFA93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E7BBF8-824E-D241-BD23-54170235E844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="Vol.4" sheetId="4" r:id="rId4"/>
     <sheet name="Vol.5" sheetId="5" r:id="rId5"/>
     <sheet name="Vol.6" sheetId="6" r:id="rId6"/>
+    <sheet name="Vol.7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="339">
   <si>
     <t>No.</t>
   </si>
@@ -36,6 +37,867 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>bloom</t>
+  </si>
+  <si>
+    <t>花がさく</t>
+  </si>
+  <si>
+    <t>cookbook</t>
+  </si>
+  <si>
+    <t>tool</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>shampoo</t>
+  </si>
+  <si>
+    <t>シャンプー</t>
+  </si>
+  <si>
+    <t>put</t>
+  </si>
+  <si>
+    <t>置（お）く</t>
+  </si>
+  <si>
+    <t>wool</t>
+  </si>
+  <si>
+    <t>羊毛</t>
+  </si>
+  <si>
+    <t>stool</t>
+  </si>
+  <si>
+    <t>スツール</t>
+  </si>
+  <si>
+    <t>proof</t>
+  </si>
+  <si>
+    <t>証（しょう）明</t>
+  </si>
+  <si>
+    <t>prove</t>
+  </si>
+  <si>
+    <t>証（しょう）明する</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>グループ</t>
+  </si>
+  <si>
+    <t>brook</t>
+  </si>
+  <si>
+    <t>小川</t>
+  </si>
+  <si>
+    <t>foolish</t>
+  </si>
+  <si>
+    <t>おろかな</t>
+  </si>
+  <si>
+    <t>bush</t>
+  </si>
+  <si>
+    <t>やぶ</t>
+  </si>
+  <si>
+    <t>crooked</t>
+  </si>
+  <si>
+    <t>曲がった</t>
+  </si>
+  <si>
+    <t>booth</t>
+  </si>
+  <si>
+    <t>ブース</t>
+  </si>
+  <si>
+    <t>raccoon</t>
+  </si>
+  <si>
+    <t>あらいぐま</t>
+  </si>
+  <si>
+    <t>hook</t>
+  </si>
+  <si>
+    <t>フック</t>
+  </si>
+  <si>
+    <t>groom</t>
+  </si>
+  <si>
+    <t>花むこ</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>屋根</t>
+  </si>
+  <si>
+    <t>soup</t>
+  </si>
+  <si>
+    <t>スープ</t>
+  </si>
+  <si>
+    <t>cartoon</t>
+  </si>
+  <si>
+    <t>まんが</t>
+  </si>
+  <si>
+    <t>choose</t>
+  </si>
+  <si>
+    <t>選（えら）ぶ</t>
+  </si>
+  <si>
+    <t>childhood</t>
+  </si>
+  <si>
+    <t>子どものころ</t>
+  </si>
+  <si>
+    <t>bookstore</t>
+  </si>
+  <si>
+    <t>本屋</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>西</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>急な・けわしい</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>メンバー・会員</t>
+  </si>
+  <si>
+    <t>gleam</t>
+  </si>
+  <si>
+    <t>きらめく・かがやく</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>新しい・新（しん）せんな</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>スピード・速さ</t>
+  </si>
+  <si>
+    <t>steam</t>
+  </si>
+  <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
+    <t>beast</t>
+  </si>
+  <si>
+    <t>けもの</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>speck</t>
+  </si>
+  <si>
+    <t>小さな点・しみ</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>持っていた</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>〜のふりをする</t>
+  </si>
+  <si>
+    <t>greed</t>
+  </si>
+  <si>
+    <t>ほしがりすぎること</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>たな</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>もっとも少ない</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>ねっしんな</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>chief</t>
+  </si>
+  <si>
+    <t>おもな・長</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>全部終わる・かんせいする</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>そで</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>エンジン</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技術（ぎじゅつ）</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>犯罪（はんざい）</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>すりつぶす</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>今夜（こんや）</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>レンガ</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光（ひかり）・軽（かる）い</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>住（す）む・生（い）きる</t>
+  </si>
+  <si>
+    <t>chill</t>
+  </si>
+  <si>
+    <t>冷（ひ）え・寒気（さむけ）</t>
+  </si>
+  <si>
+    <t>delight</t>
+  </si>
+  <si>
+    <t>大喜（おおよろこ）び</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>建（た）てる</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>みぞ</t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>決（き）める</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>目撃者（もくげきしゃ）</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>風（かぜ）・巻（ま）く</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>地区（ちく）</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>インチ</t>
+  </si>
+  <si>
+    <t>sigh</t>
+  </si>
+  <si>
+    <t>ため息</t>
+  </si>
+  <si>
+    <t>fright</t>
+  </si>
+  <si>
+    <t>恐怖（きょうふ）</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>思（おも）い出（だ）させる</t>
+  </si>
+  <si>
+    <t>splice</t>
+  </si>
+  <si>
+    <t>つなぎ合（あ）わせる</t>
+  </si>
+  <si>
+    <t>spinning</t>
+  </si>
+  <si>
+    <t>回転（かいてん）</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>チケット・切符（きっぷ）</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>驚（おどろ）き</t>
+  </si>
+  <si>
+    <t>brighten</t>
+  </si>
+  <si>
+    <t>明（あか）るくする</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>ブロック・じゃまする</t>
+  </si>
+  <si>
+    <t>shown</t>
+  </si>
+  <si>
+    <t>見せた</t>
+  </si>
+  <si>
+    <t>oatmeal</t>
+  </si>
+  <si>
+    <t>オートミール</t>
+  </si>
+  <si>
+    <t>wrote</t>
+  </si>
+  <si>
+    <t>書いた</t>
+  </si>
+  <si>
+    <t>fellow</t>
+  </si>
+  <si>
+    <t>仲（なか）間</t>
+  </si>
+  <si>
+    <t>scold</t>
+  </si>
+  <si>
+    <t>しかる</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>海岸</t>
+  </si>
+  <si>
+    <t>odd</t>
+  </si>
+  <si>
+    <t>変（へん）な</t>
+  </si>
+  <si>
+    <t>locate</t>
+  </si>
+  <si>
+    <t>見つける</t>
+  </si>
+  <si>
+    <t>slope</t>
+  </si>
+  <si>
+    <t>坂</t>
+  </si>
+  <si>
+    <t>throat</t>
+  </si>
+  <si>
+    <t>のど</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>主人（しゅじん）</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>オンライン</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>しょうげき</t>
+  </si>
+  <si>
+    <t>solve</t>
+  </si>
+  <si>
+    <t>解（と）く</t>
+  </si>
+  <si>
+    <t>known</t>
+  </si>
+  <si>
+    <t>知られた</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>在（ざい）庫</t>
+  </si>
+  <si>
+    <t>boast</t>
+  </si>
+  <si>
+    <t>じまんする</t>
+  </si>
+  <si>
+    <t>globe</t>
+  </si>
+  <si>
+    <t>地球（ちきゅう）</t>
+  </si>
+  <si>
+    <t>borrow</t>
+  </si>
+  <si>
+    <t>借（か）りる</t>
+  </si>
+  <si>
+    <t>compose</t>
+  </si>
+  <si>
+    <t>作曲する</t>
+  </si>
+  <si>
+    <t>rocket</t>
+  </si>
+  <si>
+    <t>ロケット</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>医者</t>
+  </si>
+  <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>待つ</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>重さ</t>
+  </si>
+  <si>
+    <t>heard</t>
+  </si>
+  <si>
+    <t>聞いた</t>
+  </si>
+  <si>
+    <t>herd</t>
+  </si>
+  <si>
+    <t>群（む）れ</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+  <si>
+    <t>日々</t>
+  </si>
+  <si>
+    <t>daze</t>
+  </si>
+  <si>
+    <t>ぼんやり</t>
+  </si>
+  <si>
+    <t>heel</t>
+  </si>
+  <si>
+    <t>かかと</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>治（なお）る</t>
+  </si>
+  <si>
+    <t>peak</t>
+  </si>
+  <si>
+    <t>頂上（ちょうじょう）</t>
+  </si>
+  <si>
+    <t>peek</t>
+  </si>
+  <si>
+    <t>のぞき見</t>
+  </si>
+  <si>
+    <t>sent</t>
+  </si>
+  <si>
+    <t>送った</t>
+  </si>
+  <si>
+    <t>cent</t>
+  </si>
+  <si>
+    <t>セント</t>
+  </si>
+  <si>
+    <t>scent</t>
+  </si>
+  <si>
+    <t>におい</t>
+  </si>
+  <si>
+    <t>feet</t>
+  </si>
+  <si>
+    <t>足</t>
+  </si>
+  <si>
+    <t>feat</t>
+  </si>
+  <si>
+    <t>てがら</t>
+  </si>
+  <si>
+    <t>vain</t>
+  </si>
+  <si>
+    <t>うぬぼれた</t>
+  </si>
+  <si>
+    <t>vane</t>
+  </si>
+  <si>
+    <t>羽根</t>
+  </si>
+  <si>
+    <t>vein</t>
+  </si>
+  <si>
+    <t>静脈（せいみゃく）、血管（けっかん）</t>
+  </si>
+  <si>
+    <t>miner</t>
+  </si>
+  <si>
+    <t>鉱夫（こうふ）</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>重要（じゅうよう）でない</t>
+  </si>
+  <si>
+    <t>allowed</t>
+  </si>
+  <si>
+    <t>許（ゆる）された</t>
+  </si>
+  <si>
+    <t>aloud</t>
+  </si>
+  <si>
+    <t>声に出して</t>
+  </si>
+  <si>
+    <t>who's</t>
+  </si>
+  <si>
+    <t>だれ（"who is"を短くした言葉）</t>
+  </si>
+  <si>
+    <t>whose</t>
+  </si>
+  <si>
+    <t>だれの</t>
+  </si>
+  <si>
     <t>bunch</t>
   </si>
   <si>
@@ -51,6 +913,9 @@
     <t>argue</t>
   </si>
   <si>
+    <t>議論（ぎろん）する</t>
+  </si>
+  <si>
     <t>crumb</t>
   </si>
   <si>
@@ -156,6 +1021,9 @@
     <t>undercover</t>
   </si>
   <si>
+    <t>秘密（ひみつ）の</t>
+  </si>
+  <si>
     <t>bruise</t>
   </si>
   <si>
@@ -174,730 +1042,7 @@
     <t>シチュー</t>
   </si>
   <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>steep</t>
-  </si>
-  <si>
-    <t>急な・けわしい</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>メンバー・会員</t>
-  </si>
-  <si>
-    <t>gleam</t>
-  </si>
-  <si>
-    <t>きらめく・かがやく</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>新しい・新（しん）せんな</t>
-  </si>
-  <si>
-    <t>freedom</t>
-  </si>
-  <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>スピード・速さ</t>
-  </si>
-  <si>
-    <t>steam</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
-  </si>
-  <si>
-    <t>beast</t>
-  </si>
-  <si>
-    <t>けもの</t>
-  </si>
-  <si>
-    <t>believe</t>
-  </si>
-  <si>
-    <t>しんじる</t>
-  </si>
-  <si>
-    <t>speck</t>
-  </si>
-  <si>
-    <t>小さな点・しみ</t>
-  </si>
-  <si>
-    <t>kept</t>
-  </si>
-  <si>
-    <t>持っていた</t>
-  </si>
-  <si>
-    <t>cheap</t>
-  </si>
-  <si>
-    <t>安い</t>
-  </si>
-  <si>
-    <t>pretend</t>
-  </si>
-  <si>
-    <t>〜のふりをする</t>
-  </si>
-  <si>
-    <t>greed</t>
-  </si>
-  <si>
-    <t>ほしがりすぎること</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>たな</t>
-  </si>
-  <si>
-    <t>least</t>
-  </si>
-  <si>
-    <t>もっとも少ない</t>
-  </si>
-  <si>
-    <t>eager</t>
-  </si>
-  <si>
-    <t>ねっしんな</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>理由</t>
-  </si>
-  <si>
-    <t>chief</t>
-  </si>
-  <si>
-    <t>おもな・長</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
-    <t>全部終わる・かんせいする</t>
-  </si>
-  <si>
-    <t>sleeve</t>
-  </si>
-  <si>
-    <t>そで</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>エンジン</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>守る</t>
-  </si>
-  <si>
-    <t>skill</t>
-  </si>
-  <si>
-    <t>技術（ぎじゅつ）</t>
-  </si>
-  <si>
-    <t>crime</t>
-  </si>
-  <si>
-    <t>犯罪（はんざい）</t>
-  </si>
-  <si>
-    <t>grind</t>
-  </si>
-  <si>
-    <t>すりつぶす</t>
-  </si>
-  <si>
-    <t>tonight</t>
-  </si>
-  <si>
-    <t>今夜（こんや）</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>レンガ</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
-    <t>光（ひかり）・軽（かる）い</t>
-  </si>
-  <si>
-    <t>live</t>
-  </si>
-  <si>
-    <t>住（す）む・生（い）きる</t>
-  </si>
-  <si>
-    <t>chill</t>
-  </si>
-  <si>
-    <t>冷（ひ）え・寒気（さむけ）</t>
-  </si>
-  <si>
-    <t>delight</t>
-  </si>
-  <si>
-    <t>大喜（おおよろこ）び</t>
-  </si>
-  <si>
-    <t>build</t>
-  </si>
-  <si>
-    <t>建（た）てる</t>
-  </si>
-  <si>
-    <t>ditch</t>
-  </si>
-  <si>
-    <t>みぞ</t>
-  </si>
-  <si>
-    <t>decide</t>
-  </si>
-  <si>
-    <t>決（き）める</t>
-  </si>
-  <si>
-    <t>witness</t>
-  </si>
-  <si>
-    <t>目撃者（もくげきしゃ）</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>風（かぜ）・巻（ま）く</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>地区（ちく）</t>
-  </si>
-  <si>
-    <t>inch</t>
-  </si>
-  <si>
-    <t>インチ</t>
-  </si>
-  <si>
-    <t>sigh</t>
-  </si>
-  <si>
-    <t>ため息</t>
-  </si>
-  <si>
-    <t>fright</t>
-  </si>
-  <si>
-    <t>恐怖（きょうふ）</t>
-  </si>
-  <si>
-    <t>remind</t>
-  </si>
-  <si>
-    <t>思（おも）い出（だ）させる</t>
-  </si>
-  <si>
-    <t>splice</t>
-  </si>
-  <si>
-    <t>つなぎ合（あ）わせる</t>
-  </si>
-  <si>
-    <t>spinning</t>
-  </si>
-  <si>
-    <t>回転（かいてん）</t>
-  </si>
-  <si>
-    <t>ticket</t>
-  </si>
-  <si>
-    <t>チケット・切符（きっぷ）</t>
-  </si>
-  <si>
-    <t>surprise</t>
-  </si>
-  <si>
-    <t>驚（おどろ）き</t>
-  </si>
-  <si>
-    <t>brighten</t>
-  </si>
-  <si>
-    <t>明（あか）るくする</t>
-  </si>
-  <si>
-    <t>block</t>
-  </si>
-  <si>
-    <t>ブロック・じゃまする</t>
-  </si>
-  <si>
-    <t>shown</t>
-  </si>
-  <si>
-    <t>見せた</t>
-  </si>
-  <si>
-    <t>oatmeal</t>
-  </si>
-  <si>
-    <t>オートミール</t>
-  </si>
-  <si>
-    <t>wrote</t>
-  </si>
-  <si>
-    <t>書いた</t>
-  </si>
-  <si>
-    <t>fellow</t>
-  </si>
-  <si>
-    <t>仲（なか）間</t>
-  </si>
-  <si>
-    <t>scold</t>
-  </si>
-  <si>
-    <t>しかる</t>
-  </si>
-  <si>
-    <t>coast</t>
-  </si>
-  <si>
-    <t>海岸</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>変（へん）な</t>
-  </si>
-  <si>
-    <t>locate</t>
-  </si>
-  <si>
-    <t>見つける</t>
-  </si>
-  <si>
-    <t>slope</t>
-  </si>
-  <si>
-    <t>坂</t>
-  </si>
-  <si>
-    <t>throat</t>
-  </si>
-  <si>
-    <t>のど</t>
-  </si>
-  <si>
-    <t>host</t>
-  </si>
-  <si>
-    <t>主人（しゅじん）</t>
-  </si>
-  <si>
-    <t>online</t>
-  </si>
-  <si>
-    <t>オンライン</t>
-  </si>
-  <si>
-    <t>shock</t>
-  </si>
-  <si>
-    <t>しょうげき</t>
-  </si>
-  <si>
-    <t>solve</t>
-  </si>
-  <si>
-    <t>解（と）く</t>
-  </si>
-  <si>
-    <t>known</t>
-  </si>
-  <si>
-    <t>知られた</t>
-  </si>
-  <si>
-    <t>remote</t>
-  </si>
-  <si>
-    <t>遠い</t>
-  </si>
-  <si>
-    <t>stock</t>
-  </si>
-  <si>
-    <t>在（ざい）庫</t>
-  </si>
-  <si>
-    <t>boast</t>
-  </si>
-  <si>
-    <t>じまんする</t>
-  </si>
-  <si>
-    <t>globe</t>
-  </si>
-  <si>
-    <t>地球（ちきゅう）</t>
-  </si>
-  <si>
-    <t>borrow</t>
-  </si>
-  <si>
-    <t>借（か）りる</t>
-  </si>
-  <si>
-    <t>compose</t>
-  </si>
-  <si>
-    <t>作曲する</t>
-  </si>
-  <si>
-    <t>rocket</t>
-  </si>
-  <si>
-    <t>ロケット</t>
-  </si>
-  <si>
-    <t>doctor</t>
-  </si>
-  <si>
-    <t>医者</t>
-  </si>
-  <si>
-    <t>wait</t>
-  </si>
-  <si>
-    <t>待つ</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>重さ</t>
-  </si>
-  <si>
-    <t>heard</t>
-  </si>
-  <si>
-    <t>聞いた</t>
-  </si>
-  <si>
-    <t>herd</t>
-  </si>
-  <si>
-    <t>群（む）れ</t>
-  </si>
-  <si>
-    <t>days</t>
-  </si>
-  <si>
-    <t>日々</t>
-  </si>
-  <si>
-    <t>daze</t>
-  </si>
-  <si>
-    <t>ぼんやり</t>
-  </si>
-  <si>
-    <t>heel</t>
-  </si>
-  <si>
-    <t>かかと</t>
-  </si>
-  <si>
-    <t>heal</t>
-  </si>
-  <si>
-    <t>治（なお）る</t>
-  </si>
-  <si>
-    <t>peak</t>
-  </si>
-  <si>
-    <t>頂上（ちょうじょう）</t>
-  </si>
-  <si>
-    <t>peek</t>
-  </si>
-  <si>
-    <t>のぞき見</t>
-  </si>
-  <si>
-    <t>sent</t>
-  </si>
-  <si>
-    <t>送った</t>
-  </si>
-  <si>
-    <t>cent</t>
-  </si>
-  <si>
-    <t>セント</t>
-  </si>
-  <si>
-    <t>scent</t>
-  </si>
-  <si>
-    <t>におい</t>
-  </si>
-  <si>
-    <t>feet</t>
-  </si>
-  <si>
-    <t>足</t>
-  </si>
-  <si>
-    <t>feat</t>
-  </si>
-  <si>
-    <t>てがら</t>
-  </si>
-  <si>
-    <t>vain</t>
-  </si>
-  <si>
-    <t>うぬぼれた</t>
-  </si>
-  <si>
-    <t>vane</t>
-  </si>
-  <si>
-    <t>羽根</t>
-  </si>
-  <si>
-    <t>vein</t>
-  </si>
-  <si>
-    <t>静脈（せいみゃく）、血管（けっかん）</t>
-  </si>
-  <si>
-    <t>miner</t>
-  </si>
-  <si>
-    <t>鉱夫（こうふ）</t>
-  </si>
-  <si>
-    <t>minor</t>
-  </si>
-  <si>
-    <t>重要（じゅうよう）でない</t>
-  </si>
-  <si>
-    <t>allowed</t>
-  </si>
-  <si>
-    <t>許（ゆる）された</t>
-  </si>
-  <si>
-    <t>aloud</t>
-  </si>
-  <si>
-    <t>声に出して</t>
-  </si>
-  <si>
-    <t>who's</t>
-  </si>
-  <si>
-    <t>だれ（"who is"を短くした言葉）</t>
-  </si>
-  <si>
-    <t>whose</t>
-  </si>
-  <si>
-    <t>だれの</t>
-  </si>
-  <si>
-    <t>議論（ぎろん）する</t>
-  </si>
-  <si>
-    <t>秘密（ひみつ）の</t>
+    <t>料理（りょうり）の本</t>
   </si>
 </sst>
 </file>
@@ -1296,10 +1441,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1307,10 +1452,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1318,10 +1463,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1329,10 +1474,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1340,10 +1485,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1351,10 +1496,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1362,10 +1507,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1373,10 +1518,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1384,10 +1529,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1395,10 +1540,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1406,10 +1551,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1417,10 +1562,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1428,10 +1573,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1439,10 +1584,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1450,10 +1595,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1461,10 +1606,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1472,10 +1617,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1483,10 +1628,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1494,10 +1639,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1505,10 +1650,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1516,10 +1661,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1527,10 +1672,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1538,10 +1683,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1549,10 +1694,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1581,10 +1726,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1592,10 +1737,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1603,10 +1748,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1614,10 +1759,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1625,10 +1770,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1636,10 +1781,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1647,10 +1792,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1658,10 +1803,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1669,10 +1814,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1680,10 +1825,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1691,10 +1836,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1702,10 +1847,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1713,10 +1858,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1724,10 +1869,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1735,10 +1880,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1746,10 +1891,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1757,10 +1902,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1768,10 +1913,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1779,10 +1924,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1790,10 +1935,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1801,10 +1946,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1812,10 +1957,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1823,10 +1968,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1834,10 +1979,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1866,10 +2011,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1877,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1888,10 +2033,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1899,10 +2044,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1910,10 +2055,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1921,10 +2066,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1932,10 +2077,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1943,10 +2088,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1954,10 +2099,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1965,10 +2110,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1976,10 +2121,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1987,10 +2132,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1998,10 +2143,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2009,10 +2154,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2020,10 +2165,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2031,10 +2176,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2042,10 +2187,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2053,10 +2198,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2064,10 +2209,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2075,10 +2220,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2086,10 +2231,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2097,10 +2242,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2108,10 +2253,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2119,10 +2264,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2151,10 +2296,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2162,10 +2307,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2173,10 +2318,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2184,10 +2329,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2195,10 +2340,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2206,10 +2351,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2217,10 +2362,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2228,10 +2373,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2239,10 +2384,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2250,10 +2395,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2261,10 +2406,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2272,10 +2417,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2283,10 +2428,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2294,10 +2439,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2305,10 +2450,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2316,10 +2461,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2327,10 +2472,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2338,10 +2483,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2349,10 +2494,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2360,10 +2505,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2371,10 +2516,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2382,10 +2527,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2393,10 +2538,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2404,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2436,10 +2581,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2447,10 +2592,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2458,10 +2603,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2469,10 +2614,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2480,10 +2625,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2491,10 +2636,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2502,10 +2647,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2513,10 +2658,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2524,10 +2669,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2535,10 +2680,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2546,10 +2691,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2557,10 +2702,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2568,10 +2713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2579,10 +2724,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2590,10 +2735,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2601,10 +2746,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2612,10 +2757,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2623,10 +2768,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2634,10 +2779,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2645,10 +2790,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2656,10 +2801,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2667,10 +2812,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2678,10 +2823,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2689,10 +2834,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2721,10 +2866,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2732,10 +2877,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>292</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2743,10 +2888,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2754,10 +2899,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2765,10 +2910,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2776,10 +2921,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2787,10 +2932,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2798,10 +2943,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>304</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2809,10 +2954,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>306</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2820,10 +2965,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2831,10 +2976,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>310</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2842,10 +2987,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2853,10 +2998,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>314</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2864,10 +3009,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>316</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2875,10 +3020,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2886,10 +3031,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2897,10 +3042,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>322</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2908,10 +3053,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>324</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2919,10 +3064,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>326</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2930,10 +3075,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2941,10 +3086,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>290</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2952,10 +3097,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>332</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2963,10 +3108,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>46</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2974,10 +3119,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E7BBF8-824E-D241-BD23-54170235E844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_77E5CCD9938244C218D9EDD50651143BF426EA18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="Vol.5" sheetId="5" r:id="rId5"/>
     <sheet name="Vol.6" sheetId="6" r:id="rId6"/>
     <sheet name="Vol.7" sheetId="7" r:id="rId7"/>
+    <sheet name="Vol.8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="385">
   <si>
     <t>No.</t>
   </si>
@@ -37,6 +38,1008 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>aloud</t>
+  </si>
+  <si>
+    <t>声に出して</t>
+  </si>
+  <si>
+    <t>bald</t>
+  </si>
+  <si>
+    <t>はげた</t>
+  </si>
+  <si>
+    <t>hawk</t>
+  </si>
+  <si>
+    <t>タカ</t>
+  </si>
+  <si>
+    <t>south</t>
+  </si>
+  <si>
+    <t>南</t>
+  </si>
+  <si>
+    <t>faucet</t>
+  </si>
+  <si>
+    <t>蛇口（じゃぐち）</t>
+  </si>
+  <si>
+    <t>proud</t>
+  </si>
+  <si>
+    <t>誇（ほこ）らしい</t>
+  </si>
+  <si>
+    <t>claw</t>
+  </si>
+  <si>
+    <t>つめ</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>塔（とう）・タワー</t>
+  </si>
+  <si>
+    <t>stalk</t>
+  </si>
+  <si>
+    <t>茎（くき）</t>
+  </si>
+  <si>
+    <t>couple</t>
+  </si>
+  <si>
+    <t>2人組・カップル</t>
+  </si>
+  <si>
+    <t>howl</t>
+  </si>
+  <si>
+    <t>遠ぼえする</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>まちがった・うその</t>
+  </si>
+  <si>
+    <t>dawn</t>
+  </si>
+  <si>
+    <t>夜明け</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>許（ゆる）す</t>
+  </si>
+  <si>
+    <t>drown</t>
+  </si>
+  <si>
+    <t>おぼれる</t>
+  </si>
+  <si>
+    <t>pause</t>
+  </si>
+  <si>
+    <t>一時停止（いちじていし）</t>
+  </si>
+  <si>
+    <t>fault</t>
+  </si>
+  <si>
+    <t>あやまち・〜のせい</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>原因（げんいん）</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>量（りょう）</t>
+  </si>
+  <si>
+    <t>cloudier</t>
+  </si>
+  <si>
+    <t>もっとくもった</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>作者</t>
+  </si>
+  <si>
+    <t>sprawl</t>
+  </si>
+  <si>
+    <t>手足をのばして横になる</t>
+  </si>
+  <si>
+    <t>ounce</t>
+  </si>
+  <si>
+    <t>オンス</t>
+  </si>
+  <si>
+    <t>coward</t>
+  </si>
+  <si>
+    <t>おくびょう者</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>西</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>急な・けわしい</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>メンバー・会員</t>
+  </si>
+  <si>
+    <t>gleam</t>
+  </si>
+  <si>
+    <t>きらめく・かがやく</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>新しい・新（しん）せんな</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>スピード・速さ</t>
+  </si>
+  <si>
+    <t>steam</t>
+  </si>
+  <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
+    <t>beast</t>
+  </si>
+  <si>
+    <t>けもの</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>speck</t>
+  </si>
+  <si>
+    <t>小さな点・しみ</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>持っていた</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>〜のふりをする</t>
+  </si>
+  <si>
+    <t>greed</t>
+  </si>
+  <si>
+    <t>ほしがりすぎること</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>たな</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>もっとも少ない</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>ねっしんな</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>chief</t>
+  </si>
+  <si>
+    <t>おもな・長</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>全部終わる・かんせいする</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>そで</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>エンジン</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技術（ぎじゅつ）</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>犯罪（はんざい）</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>すりつぶす</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>今夜（こんや）</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>レンガ</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光（ひかり）・軽（かる）い</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>住（す）む・生（い）きる</t>
+  </si>
+  <si>
+    <t>chill</t>
+  </si>
+  <si>
+    <t>冷（ひ）え・寒気（さむけ）</t>
+  </si>
+  <si>
+    <t>delight</t>
+  </si>
+  <si>
+    <t>大喜（おおよろこ）び</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>建（た）てる</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>みぞ</t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>決（き）める</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>目撃者（もくげきしゃ）</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>風（かぜ）・巻（ま）く</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>地区（ちく）</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>インチ</t>
+  </si>
+  <si>
+    <t>sigh</t>
+  </si>
+  <si>
+    <t>ため息</t>
+  </si>
+  <si>
+    <t>fright</t>
+  </si>
+  <si>
+    <t>恐怖（きょうふ）</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>思（おも）い出（だ）させる</t>
+  </si>
+  <si>
+    <t>splice</t>
+  </si>
+  <si>
+    <t>つなぎ合（あ）わせる</t>
+  </si>
+  <si>
+    <t>spinning</t>
+  </si>
+  <si>
+    <t>回転（かいてん）</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>チケット・切符（きっぷ）</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>驚（おどろ）き</t>
+  </si>
+  <si>
+    <t>brighten</t>
+  </si>
+  <si>
+    <t>明（あか）るくする</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>ブロック・じゃまする</t>
+  </si>
+  <si>
+    <t>shown</t>
+  </si>
+  <si>
+    <t>見せた</t>
+  </si>
+  <si>
+    <t>oatmeal</t>
+  </si>
+  <si>
+    <t>オートミール</t>
+  </si>
+  <si>
+    <t>wrote</t>
+  </si>
+  <si>
+    <t>書いた</t>
+  </si>
+  <si>
+    <t>fellow</t>
+  </si>
+  <si>
+    <t>仲（なか）間</t>
+  </si>
+  <si>
+    <t>scold</t>
+  </si>
+  <si>
+    <t>しかる</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>海岸</t>
+  </si>
+  <si>
+    <t>odd</t>
+  </si>
+  <si>
+    <t>変（へん）な</t>
+  </si>
+  <si>
+    <t>locate</t>
+  </si>
+  <si>
+    <t>見つける</t>
+  </si>
+  <si>
+    <t>slope</t>
+  </si>
+  <si>
+    <t>坂</t>
+  </si>
+  <si>
+    <t>throat</t>
+  </si>
+  <si>
+    <t>のど</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>主人（しゅじん）</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>オンライン</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>しょうげき</t>
+  </si>
+  <si>
+    <t>solve</t>
+  </si>
+  <si>
+    <t>解（と）く</t>
+  </si>
+  <si>
+    <t>known</t>
+  </si>
+  <si>
+    <t>知られた</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>在（ざい）庫</t>
+  </si>
+  <si>
+    <t>boast</t>
+  </si>
+  <si>
+    <t>じまんする</t>
+  </si>
+  <si>
+    <t>globe</t>
+  </si>
+  <si>
+    <t>地球（ちきゅう）</t>
+  </si>
+  <si>
+    <t>borrow</t>
+  </si>
+  <si>
+    <t>借（か）りる</t>
+  </si>
+  <si>
+    <t>compose</t>
+  </si>
+  <si>
+    <t>作曲する</t>
+  </si>
+  <si>
+    <t>rocket</t>
+  </si>
+  <si>
+    <t>ロケット</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>医者</t>
+  </si>
+  <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>待つ</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>重さ</t>
+  </si>
+  <si>
+    <t>heard</t>
+  </si>
+  <si>
+    <t>聞いた</t>
+  </si>
+  <si>
+    <t>herd</t>
+  </si>
+  <si>
+    <t>群（む）れ</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+  <si>
+    <t>日々</t>
+  </si>
+  <si>
+    <t>daze</t>
+  </si>
+  <si>
+    <t>ぼんやり</t>
+  </si>
+  <si>
+    <t>heel</t>
+  </si>
+  <si>
+    <t>かかと</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>治（なお）る</t>
+  </si>
+  <si>
+    <t>peak</t>
+  </si>
+  <si>
+    <t>頂上（ちょうじょう）</t>
+  </si>
+  <si>
+    <t>peek</t>
+  </si>
+  <si>
+    <t>のぞき見</t>
+  </si>
+  <si>
+    <t>sent</t>
+  </si>
+  <si>
+    <t>送った</t>
+  </si>
+  <si>
+    <t>cent</t>
+  </si>
+  <si>
+    <t>セント</t>
+  </si>
+  <si>
+    <t>scent</t>
+  </si>
+  <si>
+    <t>におい</t>
+  </si>
+  <si>
+    <t>feet</t>
+  </si>
+  <si>
+    <t>足</t>
+  </si>
+  <si>
+    <t>feat</t>
+  </si>
+  <si>
+    <t>てがら</t>
+  </si>
+  <si>
+    <t>vain</t>
+  </si>
+  <si>
+    <t>うぬぼれた</t>
+  </si>
+  <si>
+    <t>vane</t>
+  </si>
+  <si>
+    <t>羽根</t>
+  </si>
+  <si>
+    <t>vein</t>
+  </si>
+  <si>
+    <t>静脈（せいみゃく）、血管（けっかん）</t>
+  </si>
+  <si>
+    <t>miner</t>
+  </si>
+  <si>
+    <t>鉱夫（こうふ）</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>重要（じゅうよう）でない</t>
+  </si>
+  <si>
+    <t>allowed</t>
+  </si>
+  <si>
+    <t>許（ゆる）された</t>
+  </si>
+  <si>
+    <t>who's</t>
+  </si>
+  <si>
+    <t>だれ（"who is"を短くした言葉）</t>
+  </si>
+  <si>
+    <t>whose</t>
+  </si>
+  <si>
+    <t>だれの</t>
+  </si>
+  <si>
+    <t>bunch</t>
+  </si>
+  <si>
+    <t>束（たば）・房（ふさ）</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>果物（くだもの）</t>
+  </si>
+  <si>
+    <t>argue</t>
+  </si>
+  <si>
+    <t>議論（ぎろん）する</t>
+  </si>
+  <si>
+    <t>crumb</t>
+  </si>
+  <si>
+    <t>パンくず</t>
+  </si>
+  <si>
+    <t>crew</t>
+  </si>
+  <si>
+    <t>乗組員</t>
+  </si>
+  <si>
+    <t>tune</t>
+  </si>
+  <si>
+    <t>曲</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>ジュース</t>
+  </si>
+  <si>
+    <t>refuse</t>
+  </si>
+  <si>
+    <t>断（ことわ）る</t>
+  </si>
+  <si>
+    <t>truth</t>
+  </si>
+  <si>
+    <t>真実</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>若（わか）い</t>
+  </si>
+  <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>手がかり</t>
+  </si>
+  <si>
+    <t>trunk</t>
+  </si>
+  <si>
+    <t>幹（みき）</t>
+  </si>
+  <si>
+    <t>amuse</t>
+  </si>
+  <si>
+    <t>楽しませる</t>
+  </si>
+  <si>
+    <t>suit</t>
+  </si>
+  <si>
+    <t>スーツ</t>
+  </si>
+  <si>
+    <t>rude</t>
+  </si>
+  <si>
+    <t>失（しつ）礼な</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>信（しん）じる</t>
+  </si>
+  <si>
+    <t>stuck</t>
+  </si>
+  <si>
+    <t>動けなくなった</t>
+  </si>
+  <si>
+    <t>rescue</t>
+  </si>
+  <si>
+    <t>助ける</t>
+  </si>
+  <si>
+    <t>dew</t>
+  </si>
+  <si>
+    <t>つゆ</t>
+  </si>
+  <si>
+    <t>brush</t>
+  </si>
+  <si>
+    <t>ブラシ</t>
+  </si>
+  <si>
+    <t>undercover</t>
+  </si>
+  <si>
+    <t>秘密（ひみつ）の</t>
+  </si>
+  <si>
+    <t>bruise</t>
+  </si>
+  <si>
+    <t>あざ</t>
+  </si>
+  <si>
+    <t>accuse</t>
+  </si>
+  <si>
+    <t>責（せ）める</t>
+  </si>
+  <si>
+    <t>stew</t>
+  </si>
+  <si>
+    <t>シチュー</t>
+  </si>
+  <si>
     <t>bloom</t>
   </si>
   <si>
@@ -46,6 +1049,9 @@
     <t>cookbook</t>
   </si>
   <si>
+    <t>料理（りょうり）の本</t>
+  </si>
+  <si>
     <t>tool</t>
   </si>
   <si>
@@ -176,873 +1182,6 @@
   </si>
   <si>
     <t>本屋</t>
-  </si>
-  <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>steep</t>
-  </si>
-  <si>
-    <t>急な・けわしい</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>メンバー・会員</t>
-  </si>
-  <si>
-    <t>gleam</t>
-  </si>
-  <si>
-    <t>きらめく・かがやく</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>新しい・新（しん）せんな</t>
-  </si>
-  <si>
-    <t>freedom</t>
-  </si>
-  <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>スピード・速さ</t>
-  </si>
-  <si>
-    <t>steam</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
-  </si>
-  <si>
-    <t>beast</t>
-  </si>
-  <si>
-    <t>けもの</t>
-  </si>
-  <si>
-    <t>believe</t>
-  </si>
-  <si>
-    <t>しんじる</t>
-  </si>
-  <si>
-    <t>speck</t>
-  </si>
-  <si>
-    <t>小さな点・しみ</t>
-  </si>
-  <si>
-    <t>kept</t>
-  </si>
-  <si>
-    <t>持っていた</t>
-  </si>
-  <si>
-    <t>cheap</t>
-  </si>
-  <si>
-    <t>安い</t>
-  </si>
-  <si>
-    <t>pretend</t>
-  </si>
-  <si>
-    <t>〜のふりをする</t>
-  </si>
-  <si>
-    <t>greed</t>
-  </si>
-  <si>
-    <t>ほしがりすぎること</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>たな</t>
-  </si>
-  <si>
-    <t>least</t>
-  </si>
-  <si>
-    <t>もっとも少ない</t>
-  </si>
-  <si>
-    <t>eager</t>
-  </si>
-  <si>
-    <t>ねっしんな</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>理由</t>
-  </si>
-  <si>
-    <t>chief</t>
-  </si>
-  <si>
-    <t>おもな・長</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
-    <t>全部終わる・かんせいする</t>
-  </si>
-  <si>
-    <t>sleeve</t>
-  </si>
-  <si>
-    <t>そで</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>エンジン</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>守る</t>
-  </si>
-  <si>
-    <t>skill</t>
-  </si>
-  <si>
-    <t>技術（ぎじゅつ）</t>
-  </si>
-  <si>
-    <t>crime</t>
-  </si>
-  <si>
-    <t>犯罪（はんざい）</t>
-  </si>
-  <si>
-    <t>grind</t>
-  </si>
-  <si>
-    <t>すりつぶす</t>
-  </si>
-  <si>
-    <t>tonight</t>
-  </si>
-  <si>
-    <t>今夜（こんや）</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>レンガ</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
-    <t>光（ひかり）・軽（かる）い</t>
-  </si>
-  <si>
-    <t>live</t>
-  </si>
-  <si>
-    <t>住（す）む・生（い）きる</t>
-  </si>
-  <si>
-    <t>chill</t>
-  </si>
-  <si>
-    <t>冷（ひ）え・寒気（さむけ）</t>
-  </si>
-  <si>
-    <t>delight</t>
-  </si>
-  <si>
-    <t>大喜（おおよろこ）び</t>
-  </si>
-  <si>
-    <t>build</t>
-  </si>
-  <si>
-    <t>建（た）てる</t>
-  </si>
-  <si>
-    <t>ditch</t>
-  </si>
-  <si>
-    <t>みぞ</t>
-  </si>
-  <si>
-    <t>decide</t>
-  </si>
-  <si>
-    <t>決（き）める</t>
-  </si>
-  <si>
-    <t>witness</t>
-  </si>
-  <si>
-    <t>目撃者（もくげきしゃ）</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>風（かぜ）・巻（ま）く</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>地区（ちく）</t>
-  </si>
-  <si>
-    <t>inch</t>
-  </si>
-  <si>
-    <t>インチ</t>
-  </si>
-  <si>
-    <t>sigh</t>
-  </si>
-  <si>
-    <t>ため息</t>
-  </si>
-  <si>
-    <t>fright</t>
-  </si>
-  <si>
-    <t>恐怖（きょうふ）</t>
-  </si>
-  <si>
-    <t>remind</t>
-  </si>
-  <si>
-    <t>思（おも）い出（だ）させる</t>
-  </si>
-  <si>
-    <t>splice</t>
-  </si>
-  <si>
-    <t>つなぎ合（あ）わせる</t>
-  </si>
-  <si>
-    <t>spinning</t>
-  </si>
-  <si>
-    <t>回転（かいてん）</t>
-  </si>
-  <si>
-    <t>ticket</t>
-  </si>
-  <si>
-    <t>チケット・切符（きっぷ）</t>
-  </si>
-  <si>
-    <t>surprise</t>
-  </si>
-  <si>
-    <t>驚（おどろ）き</t>
-  </si>
-  <si>
-    <t>brighten</t>
-  </si>
-  <si>
-    <t>明（あか）るくする</t>
-  </si>
-  <si>
-    <t>block</t>
-  </si>
-  <si>
-    <t>ブロック・じゃまする</t>
-  </si>
-  <si>
-    <t>shown</t>
-  </si>
-  <si>
-    <t>見せた</t>
-  </si>
-  <si>
-    <t>oatmeal</t>
-  </si>
-  <si>
-    <t>オートミール</t>
-  </si>
-  <si>
-    <t>wrote</t>
-  </si>
-  <si>
-    <t>書いた</t>
-  </si>
-  <si>
-    <t>fellow</t>
-  </si>
-  <si>
-    <t>仲（なか）間</t>
-  </si>
-  <si>
-    <t>scold</t>
-  </si>
-  <si>
-    <t>しかる</t>
-  </si>
-  <si>
-    <t>coast</t>
-  </si>
-  <si>
-    <t>海岸</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>変（へん）な</t>
-  </si>
-  <si>
-    <t>locate</t>
-  </si>
-  <si>
-    <t>見つける</t>
-  </si>
-  <si>
-    <t>slope</t>
-  </si>
-  <si>
-    <t>坂</t>
-  </si>
-  <si>
-    <t>throat</t>
-  </si>
-  <si>
-    <t>のど</t>
-  </si>
-  <si>
-    <t>host</t>
-  </si>
-  <si>
-    <t>主人（しゅじん）</t>
-  </si>
-  <si>
-    <t>online</t>
-  </si>
-  <si>
-    <t>オンライン</t>
-  </si>
-  <si>
-    <t>shock</t>
-  </si>
-  <si>
-    <t>しょうげき</t>
-  </si>
-  <si>
-    <t>solve</t>
-  </si>
-  <si>
-    <t>解（と）く</t>
-  </si>
-  <si>
-    <t>known</t>
-  </si>
-  <si>
-    <t>知られた</t>
-  </si>
-  <si>
-    <t>remote</t>
-  </si>
-  <si>
-    <t>遠い</t>
-  </si>
-  <si>
-    <t>stock</t>
-  </si>
-  <si>
-    <t>在（ざい）庫</t>
-  </si>
-  <si>
-    <t>boast</t>
-  </si>
-  <si>
-    <t>じまんする</t>
-  </si>
-  <si>
-    <t>globe</t>
-  </si>
-  <si>
-    <t>地球（ちきゅう）</t>
-  </si>
-  <si>
-    <t>borrow</t>
-  </si>
-  <si>
-    <t>借（か）りる</t>
-  </si>
-  <si>
-    <t>compose</t>
-  </si>
-  <si>
-    <t>作曲する</t>
-  </si>
-  <si>
-    <t>rocket</t>
-  </si>
-  <si>
-    <t>ロケット</t>
-  </si>
-  <si>
-    <t>doctor</t>
-  </si>
-  <si>
-    <t>医者</t>
-  </si>
-  <si>
-    <t>wait</t>
-  </si>
-  <si>
-    <t>待つ</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>重さ</t>
-  </si>
-  <si>
-    <t>heard</t>
-  </si>
-  <si>
-    <t>聞いた</t>
-  </si>
-  <si>
-    <t>herd</t>
-  </si>
-  <si>
-    <t>群（む）れ</t>
-  </si>
-  <si>
-    <t>days</t>
-  </si>
-  <si>
-    <t>日々</t>
-  </si>
-  <si>
-    <t>daze</t>
-  </si>
-  <si>
-    <t>ぼんやり</t>
-  </si>
-  <si>
-    <t>heel</t>
-  </si>
-  <si>
-    <t>かかと</t>
-  </si>
-  <si>
-    <t>heal</t>
-  </si>
-  <si>
-    <t>治（なお）る</t>
-  </si>
-  <si>
-    <t>peak</t>
-  </si>
-  <si>
-    <t>頂上（ちょうじょう）</t>
-  </si>
-  <si>
-    <t>peek</t>
-  </si>
-  <si>
-    <t>のぞき見</t>
-  </si>
-  <si>
-    <t>sent</t>
-  </si>
-  <si>
-    <t>送った</t>
-  </si>
-  <si>
-    <t>cent</t>
-  </si>
-  <si>
-    <t>セント</t>
-  </si>
-  <si>
-    <t>scent</t>
-  </si>
-  <si>
-    <t>におい</t>
-  </si>
-  <si>
-    <t>feet</t>
-  </si>
-  <si>
-    <t>足</t>
-  </si>
-  <si>
-    <t>feat</t>
-  </si>
-  <si>
-    <t>てがら</t>
-  </si>
-  <si>
-    <t>vain</t>
-  </si>
-  <si>
-    <t>うぬぼれた</t>
-  </si>
-  <si>
-    <t>vane</t>
-  </si>
-  <si>
-    <t>羽根</t>
-  </si>
-  <si>
-    <t>vein</t>
-  </si>
-  <si>
-    <t>静脈（せいみゃく）、血管（けっかん）</t>
-  </si>
-  <si>
-    <t>miner</t>
-  </si>
-  <si>
-    <t>鉱夫（こうふ）</t>
-  </si>
-  <si>
-    <t>minor</t>
-  </si>
-  <si>
-    <t>重要（じゅうよう）でない</t>
-  </si>
-  <si>
-    <t>allowed</t>
-  </si>
-  <si>
-    <t>許（ゆる）された</t>
-  </si>
-  <si>
-    <t>aloud</t>
-  </si>
-  <si>
-    <t>声に出して</t>
-  </si>
-  <si>
-    <t>who's</t>
-  </si>
-  <si>
-    <t>だれ（"who is"を短くした言葉）</t>
-  </si>
-  <si>
-    <t>whose</t>
-  </si>
-  <si>
-    <t>だれの</t>
-  </si>
-  <si>
-    <t>bunch</t>
-  </si>
-  <si>
-    <t>束（たば）・房（ふさ）</t>
-  </si>
-  <si>
-    <t>fruit</t>
-  </si>
-  <si>
-    <t>果物（くだもの）</t>
-  </si>
-  <si>
-    <t>argue</t>
-  </si>
-  <si>
-    <t>議論（ぎろん）する</t>
-  </si>
-  <si>
-    <t>crumb</t>
-  </si>
-  <si>
-    <t>パンくず</t>
-  </si>
-  <si>
-    <t>crew</t>
-  </si>
-  <si>
-    <t>乗組員</t>
-  </si>
-  <si>
-    <t>tune</t>
-  </si>
-  <si>
-    <t>曲</t>
-  </si>
-  <si>
-    <t>juice</t>
-  </si>
-  <si>
-    <t>ジュース</t>
-  </si>
-  <si>
-    <t>refuse</t>
-  </si>
-  <si>
-    <t>断（ことわ）る</t>
-  </si>
-  <si>
-    <t>truth</t>
-  </si>
-  <si>
-    <t>真実</t>
-  </si>
-  <si>
-    <t>young</t>
-  </si>
-  <si>
-    <t>若（わか）い</t>
-  </si>
-  <si>
-    <t>clue</t>
-  </si>
-  <si>
-    <t>手がかり</t>
-  </si>
-  <si>
-    <t>trunk</t>
-  </si>
-  <si>
-    <t>幹（みき）</t>
-  </si>
-  <si>
-    <t>amuse</t>
-  </si>
-  <si>
-    <t>楽しませる</t>
-  </si>
-  <si>
-    <t>suit</t>
-  </si>
-  <si>
-    <t>スーツ</t>
-  </si>
-  <si>
-    <t>rude</t>
-  </si>
-  <si>
-    <t>失（しつ）礼な</t>
-  </si>
-  <si>
-    <t>trust</t>
-  </si>
-  <si>
-    <t>信（しん）じる</t>
-  </si>
-  <si>
-    <t>stuck</t>
-  </si>
-  <si>
-    <t>動けなくなった</t>
-  </si>
-  <si>
-    <t>rescue</t>
-  </si>
-  <si>
-    <t>助ける</t>
-  </si>
-  <si>
-    <t>dew</t>
-  </si>
-  <si>
-    <t>つゆ</t>
-  </si>
-  <si>
-    <t>brush</t>
-  </si>
-  <si>
-    <t>ブラシ</t>
-  </si>
-  <si>
-    <t>undercover</t>
-  </si>
-  <si>
-    <t>秘密（ひみつ）の</t>
-  </si>
-  <si>
-    <t>bruise</t>
-  </si>
-  <si>
-    <t>あざ</t>
-  </si>
-  <si>
-    <t>accuse</t>
-  </si>
-  <si>
-    <t>責（せ）める</t>
-  </si>
-  <si>
-    <t>stew</t>
-  </si>
-  <si>
-    <t>シチュー</t>
-  </si>
-  <si>
-    <t>料理（りょうり）の本</t>
   </si>
 </sst>
 </file>
@@ -1085,9 +1224,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1441,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1452,10 +1592,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1463,10 +1603,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1474,10 +1614,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1485,10 +1625,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1496,10 +1636,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1507,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1518,10 +1658,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1529,10 +1669,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1540,10 +1680,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1551,10 +1691,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1562,10 +1702,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1573,10 +1713,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1584,10 +1724,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1595,10 +1735,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1606,10 +1746,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1617,10 +1757,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1628,10 +1768,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1639,10 +1779,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1650,10 +1790,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1661,10 +1801,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1672,10 +1812,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1683,10 +1823,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1694,10 +1834,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1726,10 +1866,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1737,10 +1877,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1748,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1759,10 +1899,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1770,10 +1910,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1781,10 +1921,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1792,10 +1932,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1803,10 +1943,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1814,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1825,10 +1965,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1836,10 +1976,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1847,10 +1987,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1858,10 +1998,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1869,10 +2009,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1880,10 +2020,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1891,10 +2031,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1902,10 +2042,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1913,10 +2053,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1924,10 +2064,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1935,10 +2075,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1946,10 +2086,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1957,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1968,10 +2108,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1979,10 +2119,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2011,10 +2151,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2022,10 +2162,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2033,10 +2173,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2044,10 +2184,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2055,10 +2195,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2066,10 +2206,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2077,10 +2217,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2088,10 +2228,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2099,10 +2239,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2110,10 +2250,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2121,10 +2261,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2132,10 +2272,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2143,10 +2283,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2154,10 +2294,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2165,10 +2305,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2176,10 +2316,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2187,10 +2327,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2198,10 +2338,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2209,10 +2349,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2220,10 +2360,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2231,10 +2371,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2242,10 +2382,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2253,10 +2393,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2264,10 +2404,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2296,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2307,10 +2447,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2318,10 +2458,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2329,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2340,10 +2480,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2351,10 +2491,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2362,10 +2502,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2373,10 +2513,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2384,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2395,10 +2535,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2406,10 +2546,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2417,10 +2557,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2428,10 +2568,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2439,10 +2579,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2450,10 +2590,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2461,10 +2601,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2472,10 +2612,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2483,10 +2623,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2494,10 +2634,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2505,10 +2645,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2516,10 +2656,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2527,10 +2667,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2538,10 +2678,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2549,10 +2689,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2581,10 +2721,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2592,10 +2732,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2603,10 +2743,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2614,10 +2754,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2625,10 +2765,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2636,10 +2776,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2647,10 +2787,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2658,10 +2798,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2669,10 +2809,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2680,10 +2820,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2691,10 +2831,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2702,10 +2842,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2713,10 +2853,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2724,10 +2864,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2735,10 +2875,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2746,10 +2886,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2757,10 +2897,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2768,10 +2908,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2779,10 +2919,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2790,10 +2930,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2801,10 +2941,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2812,10 +2952,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>284</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2823,10 +2963,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2834,10 +2974,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2866,10 +3006,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2877,10 +3017,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2888,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2899,10 +3039,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2910,10 +3050,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2921,10 +3061,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2932,10 +3072,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2943,10 +3083,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2954,10 +3094,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2965,10 +3105,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2976,10 +3116,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2987,10 +3127,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2998,10 +3138,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3009,10 +3149,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3020,10 +3160,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3031,10 +3171,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3042,10 +3182,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3053,10 +3193,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3064,10 +3204,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3075,10 +3215,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3086,10 +3226,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3097,10 +3237,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3108,10 +3248,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3119,10 +3259,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3151,10 +3291,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3162,10 +3302,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3173,10 +3313,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>341</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -3184,10 +3324,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>343</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3195,10 +3335,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>345</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3206,10 +3346,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3217,10 +3357,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>349</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3228,10 +3368,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>351</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3239,10 +3379,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3250,10 +3390,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3261,10 +3401,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>357</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3272,10 +3412,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>359</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3283,10 +3423,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3294,10 +3434,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3305,10 +3445,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3316,10 +3456,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>367</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3327,10 +3467,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>369</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3338,10 +3478,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>371</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3349,10 +3489,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3360,10 +3500,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3371,10 +3511,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>377</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3382,10 +3522,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>379</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3393,10 +3533,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>381</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3404,10 +3544,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol.1" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol.7" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol.8" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol.9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol.10" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -846,6 +847,397 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>learn</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>学ぶ・習う</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>dirty</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>きたない・よごれた</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>worn</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>すり切れた</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>sore</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>痛（いた）い</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>thirst</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>のどのかわき</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>燃（も）える・やけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>記録（きろく）する・レコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>cure</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>治（なお）す</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>板・乗る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>コース・進路</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>worth</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>価値（かち）がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>early</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>早い・早く</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>帰る・返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>pure</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>純粋（じゅんすい）な</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>探（さが）す</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>worse</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>もっと悪い</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>thirteen</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>現在（げんざい）の・流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>worthwhile</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>やりがいのある</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>foreword</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>前書き・序文（じょぶん）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>研究・調査（ちょうさ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>further</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>さらに・もっと遠くへ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
